--- a/Assets/MyGame/08.DB/StatsDB.xlsx
+++ b/Assets/MyGame/08.DB/StatsDB.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gimta\Fork\one-to-one\Assets\MyGame\08.DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D673302E-67C3-4FB9-B37B-65DE52769DCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C67874F6-C7E1-4C40-B7B0-27D5B53E8588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{E0495DAE-A223-44D5-9629-39147D95F472}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -71,6 +71,10 @@
   </si>
   <si>
     <t>dog</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curGun</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -455,7 +459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2976AD11-5C37-4DAD-9C5F-251E5ACE676A}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="3" width="6.3984375" bestFit="1" customWidth="1"/>
@@ -464,7 +468,7 @@
     <col min="6" max="6" width="11.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -483,8 +487,11 @@
       <c r="F1" t="s">
         <v>4</v>
       </c>
+      <c r="G1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -492,19 +499,22 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -512,19 +522,22 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -543,8 +556,11 @@
       <c r="F4">
         <v>3</v>
       </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4</v>
       </c>
@@ -558,6 +574,9 @@
         <v>0</v>
       </c>
       <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
         <v>0</v>
       </c>
     </row>

--- a/Assets/MyGame/08.DB/StatsDB.xlsx
+++ b/Assets/MyGame/08.DB/StatsDB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gimta\Fork\one-to-one\Assets\MyGame\08.DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C67874F6-C7E1-4C40-B7B0-27D5B53E8588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C33AB086-0E2A-4EEB-BABE-DE8CCD4FE6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{E0495DAE-A223-44D5-9629-39147D95F472}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E0495DAE-A223-44D5-9629-39147D95F472}"/>
   </bookViews>
   <sheets>
     <sheet name="Stats" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -75,6 +75,18 @@
   </si>
   <si>
     <t>curGun</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BulletCount</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -459,16 +471,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2976AD11-5C37-4DAD-9C5F-251E5ACE676A}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="3" width="6.3984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.69921875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.09765625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -490,8 +503,17 @@
       <c r="G1" t="s">
         <v>9</v>
       </c>
+      <c r="H1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -513,8 +535,17 @@
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -536,8 +567,17 @@
       <c r="G3">
         <v>0</v>
       </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -559,8 +599,17 @@
       <c r="G4">
         <v>0</v>
       </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4</v>
       </c>
